--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2199"/>
+  <dimension ref="A1:K2227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88759,17 +88759,17 @@
     <row r="1983">
       <c r="A1983" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B1983" t="inlineStr">
         <is>
-          <t>DG39003</t>
+          <t>DG09011</t>
         </is>
       </c>
       <c r="C1983" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>1.890</t>
         </is>
       </c>
       <c r="D1983" t="inlineStr">
@@ -88778,22 +88778,22 @@
         </is>
       </c>
       <c r="E1983" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F1983" t="n">
         <v>0</v>
       </c>
       <c r="G1983" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1983" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I1983" t="n">
         <v>0</v>
       </c>
       <c r="J1983" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K1983" t="inlineStr">
         <is>
@@ -88809,12 +88809,12 @@
       </c>
       <c r="B1984" t="inlineStr">
         <is>
-          <t>DG39002</t>
+          <t>DG39003</t>
         </is>
       </c>
       <c r="C1984" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>2.688</t>
         </is>
       </c>
       <c r="D1984" t="inlineStr">
@@ -88823,16 +88823,16 @@
         </is>
       </c>
       <c r="E1984" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F1984" t="n">
         <v>0</v>
       </c>
       <c r="G1984" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1984" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1984" t="n">
         <v>0</v>
@@ -88854,17 +88854,17 @@
       </c>
       <c r="B1985" t="inlineStr">
         <is>
-          <t>DG34001</t>
+          <t>DG39002</t>
         </is>
       </c>
       <c r="C1985" t="inlineStr">
         <is>
-          <t>3.003</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="D1985" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E1985" t="n">
@@ -88877,13 +88877,13 @@
         <v>6</v>
       </c>
       <c r="H1985" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1985" t="n">
         <v>0</v>
       </c>
       <c r="J1985" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1985" t="inlineStr">
         <is>
@@ -88899,12 +88899,12 @@
       </c>
       <c r="B1986" t="inlineStr">
         <is>
-          <t>DG34002</t>
+          <t>DG34001</t>
         </is>
       </c>
       <c r="C1986" t="inlineStr">
         <is>
-          <t>3.068</t>
+          <t>3.003</t>
         </is>
       </c>
       <c r="D1986" t="inlineStr">
@@ -88944,27 +88944,27 @@
       </c>
       <c r="B1987" t="inlineStr">
         <is>
-          <t>DG26009</t>
+          <t>DG34002</t>
         </is>
       </c>
       <c r="C1987" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>3.068</t>
         </is>
       </c>
       <c r="D1987" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E1987" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F1987" t="n">
         <v>0</v>
       </c>
       <c r="G1987" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1987" t="n">
         <v>0</v>
@@ -88973,7 +88973,7 @@
         <v>0</v>
       </c>
       <c r="J1987" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1987" t="inlineStr">
         <is>
@@ -88989,27 +88989,27 @@
       </c>
       <c r="B1988" t="inlineStr">
         <is>
-          <t>DG26008</t>
+          <t>DG26009</t>
         </is>
       </c>
       <c r="C1988" t="inlineStr">
         <is>
-          <t>2.997</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="D1988" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E1988" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F1988" t="n">
         <v>0</v>
       </c>
       <c r="G1988" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1988" t="n">
         <v>0</v>
@@ -89018,7 +89018,7 @@
         <v>0</v>
       </c>
       <c r="J1988" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1988" t="inlineStr">
         <is>
@@ -89034,12 +89034,12 @@
       </c>
       <c r="B1989" t="inlineStr">
         <is>
-          <t>DG14003</t>
+          <t>DG26008</t>
         </is>
       </c>
       <c r="C1989" t="inlineStr">
         <is>
-          <t>3.050</t>
+          <t>2.997</t>
         </is>
       </c>
       <c r="D1989" t="inlineStr">
@@ -89048,22 +89048,22 @@
         </is>
       </c>
       <c r="E1989" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F1989" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1989" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H1989" t="n">
         <v>0</v>
       </c>
       <c r="I1989" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1989" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K1989" t="inlineStr">
         <is>
@@ -89079,12 +89079,12 @@
       </c>
       <c r="B1990" t="inlineStr">
         <is>
-          <t>DG14004</t>
+          <t>DG14003</t>
         </is>
       </c>
       <c r="C1990" t="inlineStr">
         <is>
-          <t>3.019</t>
+          <t>3.050</t>
         </is>
       </c>
       <c r="D1990" t="inlineStr">
@@ -89124,12 +89124,12 @@
       </c>
       <c r="B1991" t="inlineStr">
         <is>
-          <t>DG14005</t>
+          <t>DG14004</t>
         </is>
       </c>
       <c r="C1991" t="inlineStr">
         <is>
-          <t>2.388</t>
+          <t>3.019</t>
         </is>
       </c>
       <c r="D1991" t="inlineStr">
@@ -89138,10 +89138,10 @@
         </is>
       </c>
       <c r="E1991" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F1991" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1991" t="n">
         <v>0</v>
@@ -89150,10 +89150,10 @@
         <v>0</v>
       </c>
       <c r="I1991" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1991" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K1991" t="inlineStr">
         <is>
@@ -89164,41 +89164,41 @@
     <row r="1992">
       <c r="A1992" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B1992" t="inlineStr">
         <is>
-          <t>DG11009</t>
+          <t>DG14005</t>
         </is>
       </c>
       <c r="C1992" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>2.388</t>
         </is>
       </c>
       <c r="D1992" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E1992" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F1992" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1992" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1992" t="n">
         <v>0</v>
       </c>
       <c r="I1992" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1992" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1992" t="inlineStr">
         <is>
@@ -89209,22 +89209,22 @@
     <row r="1993">
       <c r="A1993" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B1993" t="inlineStr">
         <is>
-          <t>DG39001</t>
+          <t>DG11009</t>
         </is>
       </c>
       <c r="C1993" t="inlineStr">
         <is>
-          <t>3.024</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D1993" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E1993" t="n">
@@ -89237,13 +89237,13 @@
         <v>6</v>
       </c>
       <c r="H1993" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1993" t="n">
         <v>0</v>
       </c>
       <c r="J1993" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K1993" t="inlineStr">
         <is>
@@ -89259,17 +89259,17 @@
       </c>
       <c r="B1994" t="inlineStr">
         <is>
-          <t>DG34003</t>
+          <t>DG39001</t>
         </is>
       </c>
       <c r="C1994" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3.024</t>
         </is>
       </c>
       <c r="D1994" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E1994" t="n">
@@ -89282,13 +89282,13 @@
         <v>6</v>
       </c>
       <c r="H1994" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1994" t="n">
         <v>0</v>
       </c>
       <c r="J1994" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K1994" t="inlineStr">
         <is>
@@ -89304,12 +89304,12 @@
       </c>
       <c r="B1995" t="inlineStr">
         <is>
-          <t>DG34004</t>
+          <t>DG34003</t>
         </is>
       </c>
       <c r="C1995" t="inlineStr">
         <is>
-          <t>3.058</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="D1995" t="inlineStr">
@@ -89349,12 +89349,12 @@
       </c>
       <c r="B1996" t="inlineStr">
         <is>
-          <t>DG34005</t>
+          <t>DG34004</t>
         </is>
       </c>
       <c r="C1996" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>3.058</t>
         </is>
       </c>
       <c r="D1996" t="inlineStr">
@@ -89363,13 +89363,13 @@
         </is>
       </c>
       <c r="E1996" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F1996" t="n">
         <v>0</v>
       </c>
       <c r="G1996" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1996" t="n">
         <v>0</v>
@@ -89378,7 +89378,7 @@
         <v>0</v>
       </c>
       <c r="J1996" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1996" t="inlineStr">
         <is>
@@ -89394,27 +89394,27 @@
       </c>
       <c r="B1997" t="inlineStr">
         <is>
-          <t>DG01001</t>
+          <t>DG34005</t>
         </is>
       </c>
       <c r="C1997" t="inlineStr">
         <is>
-          <t>3.008</t>
+          <t>0.641</t>
         </is>
       </c>
       <c r="D1997" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E1997" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F1997" t="n">
         <v>0</v>
       </c>
       <c r="G1997" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1997" t="n">
         <v>0</v>
@@ -89423,7 +89423,7 @@
         <v>0</v>
       </c>
       <c r="J1997" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K1997" t="inlineStr">
         <is>
@@ -89439,12 +89439,12 @@
       </c>
       <c r="B1998" t="inlineStr">
         <is>
-          <t>DG01002</t>
+          <t>DG01001</t>
         </is>
       </c>
       <c r="C1998" t="inlineStr">
         <is>
-          <t>3.087</t>
+          <t>3.008</t>
         </is>
       </c>
       <c r="D1998" t="inlineStr">
@@ -89484,12 +89484,12 @@
       </c>
       <c r="B1999" t="inlineStr">
         <is>
-          <t>DG01003</t>
+          <t>DG01002</t>
         </is>
       </c>
       <c r="C1999" t="inlineStr">
         <is>
-          <t>3.042</t>
+          <t>3.087</t>
         </is>
       </c>
       <c r="D1999" t="inlineStr">
@@ -89524,7 +89524,7 @@
     <row r="2000">
       <c r="A2000" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2000" t="inlineStr">
@@ -89543,22 +89543,22 @@
         </is>
       </c>
       <c r="E2000" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2000" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2000" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2000" t="n">
         <v>0</v>
       </c>
       <c r="I2000" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2000" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2000" t="inlineStr">
         <is>
@@ -91999,29 +91999,29 @@
     <row r="2055">
       <c r="A2055" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2055" t="inlineStr">
         <is>
-          <t>DG32001</t>
+          <t>DG11004</t>
         </is>
       </c>
       <c r="C2055" t="inlineStr">
         <is>
-          <t>3.006</t>
+          <t>1.479</t>
         </is>
       </c>
       <c r="D2055" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2055" t="n">
         <v>0</v>
       </c>
       <c r="F2055" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G2055" t="n">
         <v>0</v>
@@ -92030,10 +92030,10 @@
         <v>0</v>
       </c>
       <c r="I2055" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2055" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2055" t="inlineStr">
         <is>
@@ -92049,12 +92049,12 @@
       </c>
       <c r="B2056" t="inlineStr">
         <is>
-          <t>DG32002</t>
+          <t>DG32001</t>
         </is>
       </c>
       <c r="C2056" t="inlineStr">
         <is>
-          <t>3.009</t>
+          <t>3.006</t>
         </is>
       </c>
       <c r="D2056" t="inlineStr">
@@ -92094,12 +92094,12 @@
       </c>
       <c r="B2057" t="inlineStr">
         <is>
-          <t>DG32003</t>
+          <t>DG32002</t>
         </is>
       </c>
       <c r="C2057" t="inlineStr">
         <is>
-          <t>3.019</t>
+          <t>3.009</t>
         </is>
       </c>
       <c r="D2057" t="inlineStr">
@@ -92139,24 +92139,24 @@
       </c>
       <c r="B2058" t="inlineStr">
         <is>
-          <t>DG09011</t>
+          <t>DG32003</t>
         </is>
       </c>
       <c r="C2058" t="inlineStr">
         <is>
-          <t>1.890</t>
+          <t>3.019</t>
         </is>
       </c>
       <c r="D2058" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2058" t="n">
         <v>0</v>
       </c>
       <c r="F2058" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2058" t="n">
         <v>0</v>
@@ -92165,10 +92165,10 @@
         <v>0</v>
       </c>
       <c r="I2058" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J2058" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2058" t="inlineStr">
         <is>
@@ -92179,29 +92179,29 @@
     <row r="2059">
       <c r="A2059" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2059" t="inlineStr">
         <is>
-          <t>DG31001</t>
+          <t>DG09011</t>
         </is>
       </c>
       <c r="C2059" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>1.890</t>
         </is>
       </c>
       <c r="D2059" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2059" t="n">
         <v>0</v>
       </c>
       <c r="F2059" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2059" t="n">
         <v>0</v>
@@ -92210,10 +92210,10 @@
         <v>0</v>
       </c>
       <c r="I2059" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2059" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2059" t="inlineStr">
         <is>
@@ -92224,29 +92224,29 @@
     <row r="2060">
       <c r="A2060" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2060" t="inlineStr">
         <is>
-          <t>DG31002</t>
+          <t>DG09011</t>
         </is>
       </c>
       <c r="C2060" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>1.890</t>
         </is>
       </c>
       <c r="D2060" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2060" t="n">
         <v>0</v>
       </c>
       <c r="F2060" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2060" t="n">
         <v>0</v>
@@ -92255,10 +92255,10 @@
         <v>0</v>
       </c>
       <c r="I2060" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2060" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2060" t="inlineStr">
         <is>
@@ -92274,12 +92274,12 @@
       </c>
       <c r="B2061" t="inlineStr">
         <is>
-          <t>DG32004</t>
+          <t>DG31001</t>
         </is>
       </c>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>3.012</t>
+          <t>3.025</t>
         </is>
       </c>
       <c r="D2061" t="inlineStr">
@@ -92319,24 +92319,24 @@
       </c>
       <c r="B2062" t="inlineStr">
         <is>
-          <t>DG18005</t>
+          <t>DG31002</t>
         </is>
       </c>
       <c r="C2062" t="inlineStr">
         <is>
-          <t>3.094</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="D2062" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2062" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2062" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2062" t="n">
         <v>0</v>
@@ -92345,7 +92345,7 @@
         <v>0</v>
       </c>
       <c r="I2062" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2062" t="n">
         <v>3</v>
@@ -92364,24 +92364,24 @@
       </c>
       <c r="B2063" t="inlineStr">
         <is>
-          <t>DG18004</t>
+          <t>DG32004</t>
         </is>
       </c>
       <c r="C2063" t="inlineStr">
         <is>
-          <t>3.109</t>
+          <t>3.012</t>
         </is>
       </c>
       <c r="D2063" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2063" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2063" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2063" t="n">
         <v>0</v>
@@ -92390,7 +92390,7 @@
         <v>0</v>
       </c>
       <c r="I2063" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2063" t="n">
         <v>3</v>
@@ -92409,12 +92409,12 @@
       </c>
       <c r="B2064" t="inlineStr">
         <is>
-          <t>DG18003</t>
+          <t>DG18005</t>
         </is>
       </c>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>3.101</t>
+          <t>3.094</t>
         </is>
       </c>
       <c r="D2064" t="inlineStr">
@@ -92449,22 +92449,22 @@
     <row r="2065">
       <c r="A2065" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2065" t="inlineStr">
         <is>
-          <t>DG22002</t>
+          <t>DG18004</t>
         </is>
       </c>
       <c r="C2065" t="inlineStr">
         <is>
-          <t>3.053</t>
+          <t>3.109</t>
         </is>
       </c>
       <c r="D2065" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2065" t="n">
@@ -92474,16 +92474,16 @@
         <v>0</v>
       </c>
       <c r="G2065" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2065" t="n">
         <v>3</v>
-      </c>
-      <c r="I2065" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2065" t="n">
-        <v>5</v>
       </c>
       <c r="K2065" t="inlineStr">
         <is>
@@ -92494,22 +92494,22 @@
     <row r="2066">
       <c r="A2066" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2066" t="inlineStr">
         <is>
-          <t>DG22001</t>
+          <t>DG18003</t>
         </is>
       </c>
       <c r="C2066" t="inlineStr">
         <is>
-          <t>3.054</t>
+          <t>3.101</t>
         </is>
       </c>
       <c r="D2066" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2066" t="n">
@@ -92519,16 +92519,16 @@
         <v>0</v>
       </c>
       <c r="G2066" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2066" t="n">
         <v>3</v>
-      </c>
-      <c r="I2066" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2066" t="n">
-        <v>6</v>
       </c>
       <c r="K2066" t="inlineStr">
         <is>
@@ -92539,41 +92539,41 @@
     <row r="2067">
       <c r="A2067" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2067" t="inlineStr">
         <is>
-          <t>DG01002</t>
+          <t>DG22002</t>
         </is>
       </c>
       <c r="C2067" t="inlineStr">
         <is>
-          <t>3.087</t>
+          <t>3.053</t>
         </is>
       </c>
       <c r="D2067" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2067" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2067" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2067" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2067" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2067" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2067" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2067" t="inlineStr">
         <is>
@@ -92584,17 +92584,17 @@
     <row r="2068">
       <c r="A2068" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2068" t="inlineStr">
         <is>
-          <t>DG04004</t>
+          <t>DG22001</t>
         </is>
       </c>
       <c r="C2068" t="inlineStr">
         <is>
-          <t>3.093</t>
+          <t>3.054</t>
         </is>
       </c>
       <c r="D2068" t="inlineStr">
@@ -92612,13 +92612,13 @@
         <v>6</v>
       </c>
       <c r="H2068" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2068" t="n">
         <v>0</v>
       </c>
       <c r="J2068" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2068" t="inlineStr">
         <is>
@@ -92629,41 +92629,41 @@
     <row r="2069">
       <c r="A2069" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2069" t="inlineStr">
         <is>
-          <t>DG04005</t>
+          <t>DG11005</t>
         </is>
       </c>
       <c r="C2069" t="inlineStr">
         <is>
-          <t>3.064</t>
+          <t>3.096</t>
         </is>
       </c>
       <c r="D2069" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2069" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2069" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2069" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2069" t="n">
         <v>0</v>
       </c>
       <c r="I2069" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2069" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2069" t="inlineStr">
         <is>
@@ -92674,41 +92674,41 @@
     <row r="2070">
       <c r="A2070" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2070" t="inlineStr">
         <is>
-          <t>DG04006</t>
+          <t>DG11006</t>
         </is>
       </c>
       <c r="C2070" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>3.084</t>
         </is>
       </c>
       <c r="D2070" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2070" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2070" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2070" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2070" t="n">
         <v>0</v>
       </c>
       <c r="I2070" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2070" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2070" t="inlineStr">
         <is>
@@ -92719,22 +92719,22 @@
     <row r="2071">
       <c r="A2071" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2071" t="inlineStr">
         <is>
-          <t>DG31003</t>
+          <t>DG11013</t>
         </is>
       </c>
       <c r="C2071" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2071" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2071" t="n">
@@ -92764,22 +92764,22 @@
     <row r="2072">
       <c r="A2072" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2072" t="inlineStr">
         <is>
-          <t>DG31004</t>
+          <t>DG11014</t>
         </is>
       </c>
       <c r="C2072" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3.036</t>
         </is>
       </c>
       <c r="D2072" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2072" t="n">
@@ -92809,29 +92809,29 @@
     <row r="2073">
       <c r="A2073" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2073" t="inlineStr">
         <is>
-          <t>DG31005</t>
+          <t>DG11015</t>
         </is>
       </c>
       <c r="C2073" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>0.450</t>
         </is>
       </c>
       <c r="D2073" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2073" t="n">
         <v>0</v>
       </c>
       <c r="F2073" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G2073" t="n">
         <v>0</v>
@@ -92840,10 +92840,10 @@
         <v>0</v>
       </c>
       <c r="I2073" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J2073" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2073" t="inlineStr">
         <is>
@@ -92859,17 +92859,17 @@
       </c>
       <c r="B2074" t="inlineStr">
         <is>
-          <t>DG32005</t>
+          <t>DG01002</t>
         </is>
       </c>
       <c r="C2074" t="inlineStr">
         <is>
-          <t>3.012</t>
+          <t>3.087</t>
         </is>
       </c>
       <c r="D2074" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>MIX</t>
         </is>
       </c>
       <c r="E2074" t="n">
@@ -92904,36 +92904,36 @@
       </c>
       <c r="B2075" t="inlineStr">
         <is>
-          <t>DG32006</t>
+          <t>DG04004</t>
         </is>
       </c>
       <c r="C2075" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>3.093</t>
         </is>
       </c>
       <c r="D2075" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2075" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2075" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2075" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2075" t="n">
         <v>0</v>
       </c>
       <c r="I2075" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2075" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2075" t="inlineStr">
         <is>
@@ -92949,36 +92949,36 @@
       </c>
       <c r="B2076" t="inlineStr">
         <is>
-          <t>DG32007</t>
+          <t>DG04005</t>
         </is>
       </c>
       <c r="C2076" t="inlineStr">
         <is>
-          <t>3.033</t>
+          <t>3.064</t>
         </is>
       </c>
       <c r="D2076" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2076" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2076" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2076" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2076" t="n">
         <v>0</v>
       </c>
       <c r="I2076" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2076" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2076" t="inlineStr">
         <is>
@@ -92989,41 +92989,41 @@
     <row r="2077">
       <c r="A2077" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2077" t="inlineStr">
         <is>
-          <t>DG31006</t>
+          <t>DG04006</t>
         </is>
       </c>
       <c r="C2077" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>0.884</t>
         </is>
       </c>
       <c r="D2077" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2077" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2077" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2077" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2077" t="n">
         <v>0</v>
       </c>
       <c r="I2077" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2077" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2077" t="inlineStr">
         <is>
@@ -93034,12 +93034,12 @@
     <row r="2078">
       <c r="A2078" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2078" t="inlineStr">
         <is>
-          <t>DG31007</t>
+          <t>DG31003</t>
         </is>
       </c>
       <c r="C2078" t="inlineStr">
@@ -93079,17 +93079,17 @@
     <row r="2079">
       <c r="A2079" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2079" t="inlineStr">
         <is>
-          <t>DG31008</t>
+          <t>DG31004</t>
         </is>
       </c>
       <c r="C2079" t="inlineStr">
         <is>
-          <t>3.023</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="D2079" t="inlineStr">
@@ -93124,17 +93124,17 @@
     <row r="2080">
       <c r="A2080" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2080" t="inlineStr">
         <is>
-          <t>DG31009</t>
+          <t>DG31005</t>
         </is>
       </c>
       <c r="C2080" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>3.025</t>
         </is>
       </c>
       <c r="D2080" t="inlineStr">
@@ -93146,7 +93146,7 @@
         <v>0</v>
       </c>
       <c r="F2080" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G2080" t="n">
         <v>0</v>
@@ -93155,10 +93155,10 @@
         <v>0</v>
       </c>
       <c r="I2080" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2080" t="n">
         <v>2</v>
-      </c>
-      <c r="J2080" t="n">
-        <v>1</v>
       </c>
       <c r="K2080" t="inlineStr">
         <is>
@@ -93169,41 +93169,41 @@
     <row r="2081">
       <c r="A2081" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2081" t="inlineStr">
         <is>
-          <t>DG20001</t>
+          <t>DG32005</t>
         </is>
       </c>
       <c r="C2081" t="inlineStr">
         <is>
-          <t>3.032</t>
+          <t>3.012</t>
         </is>
       </c>
       <c r="D2081" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2081" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2081" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2081" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2081" t="n">
         <v>0</v>
       </c>
       <c r="I2081" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2081" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2081" t="inlineStr">
         <is>
@@ -93214,41 +93214,41 @@
     <row r="2082">
       <c r="A2082" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2082" t="inlineStr">
         <is>
-          <t>DG20002</t>
+          <t>DG32006</t>
         </is>
       </c>
       <c r="C2082" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>3.047</t>
         </is>
       </c>
       <c r="D2082" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2082" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2082" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2082" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2082" t="n">
         <v>0</v>
       </c>
       <c r="I2082" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2082" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2082" t="inlineStr">
         <is>
@@ -93259,41 +93259,41 @@
     <row r="2083">
       <c r="A2083" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2083" t="inlineStr">
         <is>
-          <t>DG20003</t>
+          <t>DG32007</t>
         </is>
       </c>
       <c r="C2083" t="inlineStr">
         <is>
-          <t>3.043</t>
+          <t>3.033</t>
         </is>
       </c>
       <c r="D2083" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2083" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2083" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2083" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2083" t="n">
         <v>0</v>
       </c>
       <c r="I2083" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2083" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2083" t="inlineStr">
         <is>
@@ -93304,41 +93304,41 @@
     <row r="2084">
       <c r="A2084" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2084" t="inlineStr">
         <is>
-          <t>DG26002</t>
+          <t>DG01002</t>
         </is>
       </c>
       <c r="C2084" t="inlineStr">
         <is>
-          <t>2.992</t>
+          <t>3.087</t>
         </is>
       </c>
       <c r="D2084" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MIX</t>
         </is>
       </c>
       <c r="E2084" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2084" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2084" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2084" t="n">
         <v>0</v>
       </c>
       <c r="I2084" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2084" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2084" t="inlineStr">
         <is>
@@ -93349,41 +93349,41 @@
     <row r="2085">
       <c r="A2085" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2085" t="inlineStr">
         <is>
-          <t>DG20004</t>
+          <t>DG01003</t>
         </is>
       </c>
       <c r="C2085" t="inlineStr">
         <is>
-          <t>3.043</t>
+          <t>3.042</t>
         </is>
       </c>
       <c r="D2085" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MIX</t>
         </is>
       </c>
       <c r="E2085" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2085" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2085" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2085" t="n">
         <v>0</v>
       </c>
       <c r="I2085" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2085" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2085" t="inlineStr">
         <is>
@@ -93394,17 +93394,17 @@
     <row r="2086">
       <c r="A2086" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2086" t="inlineStr">
         <is>
-          <t>DG20005</t>
+          <t>DG18001</t>
         </is>
       </c>
       <c r="C2086" t="inlineStr">
         <is>
-          <t>3.044</t>
+          <t>1.747</t>
         </is>
       </c>
       <c r="D2086" t="inlineStr">
@@ -93413,13 +93413,13 @@
         </is>
       </c>
       <c r="E2086" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F2086" t="n">
         <v>0</v>
       </c>
       <c r="G2086" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2086" t="n">
         <v>0</v>
@@ -93428,7 +93428,7 @@
         <v>0</v>
       </c>
       <c r="J2086" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2086" t="inlineStr">
         <is>
@@ -93439,41 +93439,41 @@
     <row r="2087">
       <c r="A2087" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2087" t="inlineStr">
         <is>
-          <t>DG34001</t>
+          <t>DG18002</t>
         </is>
       </c>
       <c r="C2087" t="inlineStr">
         <is>
-          <t>3.003</t>
+          <t>3.014</t>
         </is>
       </c>
       <c r="D2087" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2087" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2087" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2087" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2087" t="n">
         <v>0</v>
       </c>
       <c r="I2087" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2087" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2087" t="inlineStr">
         <is>
@@ -93484,22 +93484,22 @@
     <row r="2088">
       <c r="A2088" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2088" t="inlineStr">
         <is>
-          <t>DG34002</t>
+          <t>DG31006</t>
         </is>
       </c>
       <c r="C2088" t="inlineStr">
         <is>
-          <t>3.068</t>
+          <t>3.025</t>
         </is>
       </c>
       <c r="D2088" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2088" t="n">
@@ -93529,41 +93529,41 @@
     <row r="2089">
       <c r="A2089" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2089" t="inlineStr">
         <is>
-          <t>DG26005</t>
+          <t>DG31007</t>
         </is>
       </c>
       <c r="C2089" t="inlineStr">
         <is>
-          <t>2.996</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="D2089" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2089" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2089" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2089" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2089" t="n">
         <v>0</v>
       </c>
       <c r="I2089" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2089" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2089" t="inlineStr">
         <is>
@@ -93574,41 +93574,41 @@
     <row r="2090">
       <c r="A2090" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2090" t="inlineStr">
         <is>
-          <t>DG26006</t>
+          <t>DG31008</t>
         </is>
       </c>
       <c r="C2090" t="inlineStr">
         <is>
-          <t>2.996</t>
+          <t>3.023</t>
         </is>
       </c>
       <c r="D2090" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2090" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2090" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2090" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2090" t="n">
         <v>0</v>
       </c>
       <c r="I2090" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2090" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2090" t="inlineStr">
         <is>
@@ -93619,41 +93619,41 @@
     <row r="2091">
       <c r="A2091" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2091" t="inlineStr">
         <is>
-          <t>DG26007</t>
+          <t>DG31009</t>
         </is>
       </c>
       <c r="C2091" t="inlineStr">
         <is>
-          <t>2.996</t>
+          <t>0.845</t>
         </is>
       </c>
       <c r="D2091" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2091" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2091" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2091" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2091" t="n">
         <v>0</v>
       </c>
       <c r="I2091" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2091" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2091" t="inlineStr">
         <is>
@@ -93664,41 +93664,41 @@
     <row r="2092">
       <c r="A2092" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2092" t="inlineStr">
         <is>
-          <t>DG26008</t>
+          <t>DG01004</t>
         </is>
       </c>
       <c r="C2092" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>3.022</t>
         </is>
       </c>
       <c r="D2092" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MIX</t>
         </is>
       </c>
       <c r="E2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2092" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2092" t="n">
         <v>3</v>
-      </c>
-      <c r="F2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2092" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2092" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2092" t="n">
-        <v>1</v>
       </c>
       <c r="K2092" t="inlineStr">
         <is>
@@ -93709,12 +93709,12 @@
     <row r="2093">
       <c r="A2093" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2093" t="inlineStr">
         <is>
-          <t>DG20006</t>
+          <t>DG01005</t>
         </is>
       </c>
       <c r="C2093" t="inlineStr">
@@ -93724,26 +93724,26 @@
       </c>
       <c r="D2093" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MIX</t>
         </is>
       </c>
       <c r="E2093" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2093" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2093" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2093" t="n">
         <v>0</v>
       </c>
       <c r="I2093" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2093" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2093" t="inlineStr">
         <is>
@@ -93754,41 +93754,41 @@
     <row r="2094">
       <c r="A2094" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2094" t="inlineStr">
         <is>
-          <t>DG20007</t>
+          <t>DG01006</t>
         </is>
       </c>
       <c r="C2094" t="inlineStr">
         <is>
-          <t>3.039</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="D2094" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MIX</t>
         </is>
       </c>
       <c r="E2094" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2094" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2094" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2094" t="n">
         <v>0</v>
       </c>
       <c r="I2094" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2094" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2094" t="inlineStr">
         <is>
@@ -93799,41 +93799,41 @@
     <row r="2095">
       <c r="A2095" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2095" t="inlineStr">
         <is>
-          <t>DG20008</t>
+          <t>DG01007</t>
         </is>
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>1.668</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="D2095" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MIX</t>
         </is>
       </c>
       <c r="E2095" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F2095" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2095" t="n">
         <v>4</v>
       </c>
-      <c r="H2095" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2095" t="n">
-        <v>0</v>
-      </c>
       <c r="J2095" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2095" t="inlineStr">
         <is>
@@ -93844,41 +93844,41 @@
     <row r="2096">
       <c r="A2096" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2096" t="inlineStr">
         <is>
-          <t>DG34003</t>
+          <t>DG20001</t>
         </is>
       </c>
       <c r="C2096" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3.032</t>
         </is>
       </c>
       <c r="D2096" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2096" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2096" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2096" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2096" t="n">
         <v>0</v>
       </c>
       <c r="I2096" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2096" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2096" t="inlineStr">
         <is>
@@ -93889,41 +93889,41 @@
     <row r="2097">
       <c r="A2097" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2097" t="inlineStr">
         <is>
-          <t>DG34004</t>
+          <t>DG20002</t>
         </is>
       </c>
       <c r="C2097" t="inlineStr">
         <is>
-          <t>3.058</t>
+          <t>3.001</t>
         </is>
       </c>
       <c r="D2097" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2097" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2097" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2097" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2097" t="n">
         <v>0</v>
       </c>
       <c r="I2097" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2097" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2097" t="inlineStr">
         <is>
@@ -93934,41 +93934,41 @@
     <row r="2098">
       <c r="A2098" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2098" t="inlineStr">
         <is>
-          <t>DG34005</t>
+          <t>DG20003</t>
         </is>
       </c>
       <c r="C2098" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>3.043</t>
         </is>
       </c>
       <c r="D2098" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2098" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2098" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2098" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2098" t="n">
         <v>0</v>
       </c>
       <c r="I2098" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2098" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2098" t="inlineStr">
         <is>
@@ -93979,22 +93979,22 @@
     <row r="2099">
       <c r="A2099" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2099" t="inlineStr">
         <is>
-          <t>DG25001</t>
+          <t>DG26002</t>
         </is>
       </c>
       <c r="C2099" t="inlineStr">
         <is>
-          <t>3.097</t>
+          <t>2.992</t>
         </is>
       </c>
       <c r="D2099" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2099" t="n">
@@ -94024,41 +94024,41 @@
     <row r="2100">
       <c r="A2100" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2100" t="inlineStr">
         <is>
-          <t>DG25002</t>
+          <t>DG11009</t>
         </is>
       </c>
       <c r="C2100" t="inlineStr">
         <is>
-          <t>3.118</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2100" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2100" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2100" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2100" t="n">
         <v>0</v>
       </c>
       <c r="I2100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2100" t="inlineStr">
         <is>
@@ -94069,41 +94069,41 @@
     <row r="2101">
       <c r="A2101" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2101" t="inlineStr">
         <is>
-          <t>DG25003</t>
+          <t>DG11010</t>
         </is>
       </c>
       <c r="C2101" t="inlineStr">
         <is>
-          <t>3.136</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2101" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2101" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2101" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2101" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2101" t="n">
         <v>0</v>
       </c>
       <c r="I2101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2101" t="inlineStr">
         <is>
@@ -94114,41 +94114,41 @@
     <row r="2102">
       <c r="A2102" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2102" t="inlineStr">
         <is>
-          <t>DG25004</t>
+          <t>DG11011</t>
         </is>
       </c>
       <c r="C2102" t="inlineStr">
         <is>
-          <t>3.136</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2102" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2102" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2102" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2102" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2102" t="n">
         <v>0</v>
       </c>
       <c r="I2102" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2102" t="inlineStr">
         <is>
@@ -94159,41 +94159,41 @@
     <row r="2103">
       <c r="A2103" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2103" t="inlineStr">
         <is>
-          <t>DG25005</t>
+          <t>DG11012</t>
         </is>
       </c>
       <c r="C2103" t="inlineStr">
         <is>
-          <t>3.0141</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2103" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2103" t="n">
         <v>0</v>
       </c>
       <c r="I2103" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2103" t="inlineStr">
         <is>
@@ -94204,17 +94204,17 @@
     <row r="2104">
       <c r="A2104" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2104" t="inlineStr">
         <is>
-          <t>DG25006</t>
+          <t>DG20004</t>
         </is>
       </c>
       <c r="C2104" t="inlineStr">
         <is>
-          <t>2.697</t>
+          <t>3.043</t>
         </is>
       </c>
       <c r="D2104" t="inlineStr">
@@ -94223,22 +94223,22 @@
         </is>
       </c>
       <c r="E2104" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2104" t="n">
         <v>0</v>
       </c>
       <c r="G2104" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2104" t="n">
         <v>5</v>
-      </c>
-      <c r="H2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2104" t="n">
-        <v>4</v>
       </c>
       <c r="K2104" t="inlineStr">
         <is>
@@ -94249,41 +94249,41 @@
     <row r="2105">
       <c r="A2105" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2105" t="inlineStr">
         <is>
-          <t>DG36001</t>
+          <t>DG20005</t>
         </is>
       </c>
       <c r="C2105" t="inlineStr">
         <is>
-          <t>3.016</t>
+          <t>3.044</t>
         </is>
       </c>
       <c r="D2105" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2105" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2105" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2105" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2105" t="n">
         <v>0</v>
       </c>
       <c r="I2105" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2105" t="inlineStr">
         <is>
@@ -94294,22 +94294,22 @@
     <row r="2106">
       <c r="A2106" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2106" t="inlineStr">
         <is>
-          <t>DG36002</t>
+          <t>DG34001</t>
         </is>
       </c>
       <c r="C2106" t="inlineStr">
         <is>
-          <t>3.015</t>
+          <t>3.003</t>
         </is>
       </c>
       <c r="D2106" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2106" t="n">
@@ -94339,22 +94339,22 @@
     <row r="2107">
       <c r="A2107" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2107" t="inlineStr">
         <is>
-          <t>DG36003</t>
+          <t>DG34002</t>
         </is>
       </c>
       <c r="C2107" t="inlineStr">
         <is>
-          <t>3.016</t>
+          <t>3.068</t>
         </is>
       </c>
       <c r="D2107" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2107" t="n">
@@ -94384,17 +94384,17 @@
     <row r="2108">
       <c r="A2108" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2108" t="inlineStr">
         <is>
-          <t>DG36004</t>
+          <t>DG26005</t>
         </is>
       </c>
       <c r="C2108" t="inlineStr">
         <is>
-          <t>2.078</t>
+          <t>2.996</t>
         </is>
       </c>
       <c r="D2108" t="inlineStr">
@@ -94403,22 +94403,22 @@
         </is>
       </c>
       <c r="E2108" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2108" t="n">
         <v>5</v>
-      </c>
-      <c r="G2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2108" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2108" t="n">
-        <v>2</v>
       </c>
       <c r="K2108" t="inlineStr">
         <is>
@@ -94429,12 +94429,12 @@
     <row r="2109">
       <c r="A2109" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2109" t="inlineStr">
         <is>
-          <t>DG26003</t>
+          <t>DG26006</t>
         </is>
       </c>
       <c r="C2109" t="inlineStr">
@@ -94444,7 +94444,7 @@
       </c>
       <c r="D2109" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2109" t="n">
@@ -94474,38 +94474,38 @@
     <row r="2110">
       <c r="A2110" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2110" t="inlineStr">
         <is>
-          <t>DG35001</t>
+          <t>DG26007</t>
         </is>
       </c>
       <c r="C2110" t="inlineStr">
         <is>
-          <t>3.029</t>
+          <t>2.996</t>
         </is>
       </c>
       <c r="D2110" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2110" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2110" t="n">
         <v>0</v>
       </c>
       <c r="I2110" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2110" t="n">
         <v>4</v>
@@ -94519,41 +94519,41 @@
     <row r="2111">
       <c r="A2111" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2111" t="inlineStr">
         <is>
-          <t>DG35002</t>
+          <t>DG26008</t>
         </is>
       </c>
       <c r="C2111" t="inlineStr">
         <is>
-          <t>3.017</t>
+          <t>0.084</t>
         </is>
       </c>
       <c r="D2111" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2111" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2111" t="n">
         <v>0</v>
       </c>
       <c r="I2111" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2111" t="inlineStr">
         <is>
@@ -94564,17 +94564,17 @@
     <row r="2112">
       <c r="A2112" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2112" t="inlineStr">
         <is>
-          <t>DG35003</t>
+          <t>DG20006</t>
         </is>
       </c>
       <c r="C2112" t="inlineStr">
         <is>
-          <t>3.041</t>
+          <t>3.042</t>
         </is>
       </c>
       <c r="D2112" t="inlineStr">
@@ -94583,22 +94583,22 @@
         </is>
       </c>
       <c r="E2112" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2112" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2112" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2112" t="n">
         <v>0</v>
       </c>
       <c r="I2112" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2112" t="inlineStr">
         <is>
@@ -94609,17 +94609,17 @@
     <row r="2113">
       <c r="A2113" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2113" t="inlineStr">
         <is>
-          <t>DG35004</t>
+          <t>DG20007</t>
         </is>
       </c>
       <c r="C2113" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>3.039</t>
         </is>
       </c>
       <c r="D2113" t="inlineStr">
@@ -94628,22 +94628,22 @@
         </is>
       </c>
       <c r="E2113" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2113" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2113" t="n">
         <v>0</v>
       </c>
       <c r="I2113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2113" t="inlineStr">
         <is>
@@ -94654,17 +94654,17 @@
     <row r="2114">
       <c r="A2114" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2114" t="inlineStr">
         <is>
-          <t>DG29001</t>
+          <t>DG20008</t>
         </is>
       </c>
       <c r="C2114" t="inlineStr">
         <is>
-          <t>2.812</t>
+          <t>1.668</t>
         </is>
       </c>
       <c r="D2114" t="inlineStr">
@@ -94673,13 +94673,13 @@
         </is>
       </c>
       <c r="E2114" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F2114" t="n">
         <v>0</v>
       </c>
       <c r="G2114" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2114" t="n">
         <v>0</v>
@@ -94688,7 +94688,7 @@
         <v>0</v>
       </c>
       <c r="J2114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2114" t="inlineStr">
         <is>
@@ -94699,41 +94699,41 @@
     <row r="2115">
       <c r="A2115" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2115" t="inlineStr">
         <is>
-          <t>DG29002</t>
+          <t>DG34003</t>
         </is>
       </c>
       <c r="C2115" t="inlineStr">
         <is>
-          <t>2.807</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="D2115" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2115" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2115" t="n">
         <v>0</v>
       </c>
       <c r="I2115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2115" t="inlineStr">
         <is>
@@ -94744,41 +94744,41 @@
     <row r="2116">
       <c r="A2116" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2116" t="inlineStr">
         <is>
-          <t>DG29003</t>
+          <t>DG34004</t>
         </is>
       </c>
       <c r="C2116" t="inlineStr">
         <is>
-          <t>2.804</t>
+          <t>3.058</t>
         </is>
       </c>
       <c r="D2116" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2116" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2116" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2116" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2116" t="n">
         <v>0</v>
       </c>
       <c r="I2116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2116" t="inlineStr">
         <is>
@@ -94789,41 +94789,41 @@
     <row r="2117">
       <c r="A2117" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2117" t="inlineStr">
         <is>
-          <t>DG26004</t>
+          <t>DG34005</t>
         </is>
       </c>
       <c r="C2117" t="inlineStr">
         <is>
-          <t>2.997</t>
+          <t>0.446</t>
         </is>
       </c>
       <c r="D2117" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2117" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F2117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2117" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2117" t="n">
         <v>0</v>
       </c>
       <c r="I2117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2117" t="inlineStr">
         <is>
@@ -94834,22 +94834,22 @@
     <row r="2118">
       <c r="A2118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2118" t="inlineStr">
         <is>
-          <t>DG39003</t>
+          <t>DG11007</t>
         </is>
       </c>
       <c r="C2118" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2118" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2118" t="n">
@@ -94879,22 +94879,22 @@
     <row r="2119">
       <c r="A2119" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2119" t="inlineStr">
         <is>
-          <t>DG32007</t>
+          <t>DG11008</t>
         </is>
       </c>
       <c r="C2119" t="inlineStr">
         <is>
-          <t>3.033</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2119" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2119" t="n">
@@ -94910,7 +94910,7 @@
         <v>0</v>
       </c>
       <c r="I2119" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2119" t="n">
         <v>3</v>
@@ -94924,41 +94924,41 @@
     <row r="2120">
       <c r="A2120" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2120" t="inlineStr">
         <is>
-          <t>DG32006</t>
+          <t>DG25001</t>
         </is>
       </c>
       <c r="C2120" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>3.097</t>
         </is>
       </c>
       <c r="D2120" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2120" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2120" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2120" t="n">
         <v>0</v>
       </c>
       <c r="I2120" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2120" t="inlineStr">
         <is>
@@ -94969,41 +94969,41 @@
     <row r="2121">
       <c r="A2121" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2121" t="inlineStr">
         <is>
-          <t>DG31001</t>
+          <t>DG25002</t>
         </is>
       </c>
       <c r="C2121" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>3.118</t>
         </is>
       </c>
       <c r="D2121" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2121" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2121" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2121" t="n">
         <v>0</v>
       </c>
       <c r="I2121" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2121" t="inlineStr">
         <is>
@@ -95014,22 +95014,22 @@
     <row r="2122">
       <c r="A2122" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2122" t="inlineStr">
         <is>
-          <t>DG27001</t>
+          <t>DG01001</t>
         </is>
       </c>
       <c r="C2122" t="inlineStr">
         <is>
-          <t>3.108</t>
+          <t>3.008</t>
         </is>
       </c>
       <c r="D2122" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MIX</t>
         </is>
       </c>
       <c r="E2122" t="n">
@@ -95059,41 +95059,41 @@
     <row r="2123">
       <c r="A2123" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2123" t="inlineStr">
         <is>
-          <t>DG27002</t>
+          <t>DG25003</t>
         </is>
       </c>
       <c r="C2123" t="inlineStr">
         <is>
-          <t>3.126</t>
+          <t>3.136</t>
         </is>
       </c>
       <c r="D2123" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2123" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2123" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2123" t="n">
         <v>0</v>
       </c>
       <c r="I2123" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2123" t="inlineStr">
         <is>
@@ -95104,17 +95104,17 @@
     <row r="2124">
       <c r="A2124" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2124" t="inlineStr">
         <is>
-          <t>DG20001</t>
+          <t>DG25004</t>
         </is>
       </c>
       <c r="C2124" t="inlineStr">
         <is>
-          <t>3.032</t>
+          <t>3.136</t>
         </is>
       </c>
       <c r="D2124" t="inlineStr">
@@ -95123,22 +95123,22 @@
         </is>
       </c>
       <c r="E2124" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2124" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2124" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2124" t="n">
         <v>0</v>
       </c>
       <c r="I2124" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2124" t="inlineStr">
         <is>
@@ -95149,17 +95149,17 @@
     <row r="2125">
       <c r="A2125" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2125" t="inlineStr">
         <is>
-          <t>DG20002</t>
+          <t>DG25005</t>
         </is>
       </c>
       <c r="C2125" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>3.0141</t>
         </is>
       </c>
       <c r="D2125" t="inlineStr">
@@ -95168,22 +95168,22 @@
         </is>
       </c>
       <c r="E2125" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2125" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2125" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2125" t="n">
         <v>0</v>
       </c>
       <c r="I2125" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2125" t="inlineStr">
         <is>
@@ -95194,17 +95194,17 @@
     <row r="2126">
       <c r="A2126" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>DG20003</t>
+          <t>DG25006</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
         <is>
-          <t>3.043</t>
+          <t>2.697</t>
         </is>
       </c>
       <c r="D2126" t="inlineStr">
@@ -95213,22 +95213,22 @@
         </is>
       </c>
       <c r="E2126" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2126" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2126" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2126" t="n">
         <v>0</v>
       </c>
       <c r="I2126" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2126" t="inlineStr">
         <is>
@@ -95239,17 +95239,17 @@
     <row r="2127">
       <c r="A2127" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>DG27003</t>
+          <t>DG36001</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>3.016</t>
         </is>
       </c>
       <c r="D2127" t="inlineStr">
@@ -95273,7 +95273,7 @@
         <v>7</v>
       </c>
       <c r="J2127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2127" t="inlineStr">
         <is>
@@ -95284,22 +95284,22 @@
     <row r="2128">
       <c r="A2128" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2128" t="inlineStr">
         <is>
-          <t>DG31002</t>
+          <t>DG36002</t>
         </is>
       </c>
       <c r="C2128" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3.015</t>
         </is>
       </c>
       <c r="D2128" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2128" t="n">
@@ -95315,7 +95315,7 @@
         <v>0</v>
       </c>
       <c r="I2128" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2128" t="n">
         <v>3</v>
@@ -95329,17 +95329,17 @@
     <row r="2129">
       <c r="A2129" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2129" t="inlineStr">
         <is>
-          <t>DG39002</t>
+          <t>DG36003</t>
         </is>
       </c>
       <c r="C2129" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3.016</t>
         </is>
       </c>
       <c r="D2129" t="inlineStr">
@@ -95363,7 +95363,7 @@
         <v>7</v>
       </c>
       <c r="J2129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2129" t="inlineStr">
         <is>
@@ -95374,29 +95374,29 @@
     <row r="2130">
       <c r="A2130" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2130" t="inlineStr">
         <is>
-          <t>DG11001</t>
+          <t>DG36004</t>
         </is>
       </c>
       <c r="C2130" t="inlineStr">
         <is>
-          <t>3.056</t>
+          <t>2.078</t>
         </is>
       </c>
       <c r="D2130" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2130" t="n">
         <v>0</v>
       </c>
       <c r="F2130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2130" t="n">
         <v>0</v>
@@ -95405,10 +95405,10 @@
         <v>0</v>
       </c>
       <c r="I2130" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J2130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2130" t="inlineStr">
         <is>
@@ -95419,41 +95419,41 @@
     <row r="2131">
       <c r="A2131" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2131" t="inlineStr">
         <is>
-          <t>DG11002</t>
+          <t>DG26003</t>
         </is>
       </c>
       <c r="C2131" t="inlineStr">
         <is>
-          <t>3.074</t>
+          <t>2.996</t>
         </is>
       </c>
       <c r="D2131" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2131" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2131" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2131" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2131" t="n">
         <v>0</v>
       </c>
       <c r="I2131" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2131" t="inlineStr">
         <is>
@@ -95464,22 +95464,22 @@
     <row r="2132">
       <c r="A2132" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2132" t="inlineStr">
         <is>
-          <t>DG11003</t>
+          <t>DG12006</t>
         </is>
       </c>
       <c r="C2132" t="inlineStr">
         <is>
-          <t>3.037</t>
+          <t>3.077</t>
         </is>
       </c>
       <c r="D2132" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2132" t="n">
@@ -95495,7 +95495,7 @@
         <v>0</v>
       </c>
       <c r="I2132" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2132" t="n">
         <v>3</v>
@@ -95509,41 +95509,41 @@
     <row r="2133">
       <c r="A2133" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2133" t="inlineStr">
         <is>
-          <t>DG11004</t>
+          <t>DG12007</t>
         </is>
       </c>
       <c r="C2133" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>3.158</t>
         </is>
       </c>
       <c r="D2133" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2133" t="n">
         <v>0</v>
       </c>
       <c r="F2133" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2133" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2133" t="n">
         <v>3</v>
-      </c>
-      <c r="G2133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2133" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2133" t="n">
-        <v>2</v>
       </c>
       <c r="K2133" t="inlineStr">
         <is>
@@ -95554,29 +95554,29 @@
     <row r="2134">
       <c r="A2134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2134" t="inlineStr">
         <is>
-          <t>DG11005</t>
+          <t>DG12008</t>
         </is>
       </c>
       <c r="C2134" t="inlineStr">
         <is>
-          <t>3.096</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="D2134" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2134" t="n">
         <v>0</v>
       </c>
       <c r="F2134" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2134" t="n">
         <v>0</v>
@@ -95585,10 +95585,10 @@
         <v>0</v>
       </c>
       <c r="I2134" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2134" t="inlineStr">
         <is>
@@ -95599,22 +95599,22 @@
     <row r="2135">
       <c r="A2135" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2135" t="inlineStr">
         <is>
-          <t>DG11005</t>
+          <t>DG37003</t>
         </is>
       </c>
       <c r="C2135" t="inlineStr">
         <is>
-          <t>3.096</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="D2135" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2135" t="n">
@@ -95630,7 +95630,7 @@
         <v>0</v>
       </c>
       <c r="I2135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2135" t="n">
         <v>3</v>
@@ -95644,29 +95644,29 @@
     <row r="2136">
       <c r="A2136" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2136" t="inlineStr">
         <is>
-          <t>DG11006</t>
+          <t>DG37004</t>
         </is>
       </c>
       <c r="C2136" t="inlineStr">
         <is>
-          <t>3.084</t>
+          <t>1.349</t>
         </is>
       </c>
       <c r="D2136" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2136" t="n">
         <v>0</v>
       </c>
       <c r="F2136" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G2136" t="n">
         <v>0</v>
@@ -95675,10 +95675,10 @@
         <v>0</v>
       </c>
       <c r="I2136" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2136" t="inlineStr">
         <is>
@@ -95689,22 +95689,22 @@
     <row r="2137">
       <c r="A2137" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2137" t="inlineStr">
         <is>
-          <t>DG11006</t>
+          <t>DG02001</t>
         </is>
       </c>
       <c r="C2137" t="inlineStr">
         <is>
-          <t>3.084</t>
+          <t>2.937</t>
         </is>
       </c>
       <c r="D2137" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2137" t="n">
@@ -95714,16 +95714,16 @@
         <v>6</v>
       </c>
       <c r="G2137" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2137" t="n">
         <v>0</v>
       </c>
       <c r="I2137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2137" t="inlineStr">
         <is>
@@ -95734,22 +95734,22 @@
     <row r="2138">
       <c r="A2138" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2138" t="inlineStr">
         <is>
-          <t>DG11007</t>
+          <t>DG02002</t>
         </is>
       </c>
       <c r="C2138" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>2.942</t>
         </is>
       </c>
       <c r="D2138" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2138" t="n">
@@ -95759,7 +95759,7 @@
         <v>6</v>
       </c>
       <c r="G2138" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2138" t="n">
         <v>0</v>
@@ -95768,7 +95768,7 @@
         <v>7</v>
       </c>
       <c r="J2138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2138" t="inlineStr">
         <is>
@@ -95779,22 +95779,22 @@
     <row r="2139">
       <c r="A2139" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2139" t="inlineStr">
         <is>
-          <t>DG11007</t>
+          <t>DG37001</t>
         </is>
       </c>
       <c r="C2139" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.025</t>
         </is>
       </c>
       <c r="D2139" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2139" t="n">
@@ -95810,7 +95810,7 @@
         <v>0</v>
       </c>
       <c r="I2139" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2139" t="n">
         <v>3</v>
@@ -95824,22 +95824,22 @@
     <row r="2140">
       <c r="A2140" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2140" t="inlineStr">
         <is>
-          <t>DG11008</t>
+          <t>DG37002</t>
         </is>
       </c>
       <c r="C2140" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.035</t>
         </is>
       </c>
       <c r="D2140" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2140" t="n">
@@ -95869,22 +95869,22 @@
     <row r="2141">
       <c r="A2141" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2141" t="inlineStr">
         <is>
-          <t>DG11008</t>
+          <t>DG02003</t>
         </is>
       </c>
       <c r="C2141" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.004</t>
         </is>
       </c>
       <c r="D2141" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2141" t="n">
@@ -95894,16 +95894,16 @@
         <v>6</v>
       </c>
       <c r="G2141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2141" t="n">
         <v>0</v>
       </c>
       <c r="I2141" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2141" t="inlineStr">
         <is>
@@ -95914,41 +95914,41 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">
         <is>
-          <t>DG11009</t>
+          <t>DG08001</t>
         </is>
       </c>
       <c r="C2142" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.081</t>
         </is>
       </c>
       <c r="D2142" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2142" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2142" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2142" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2142" t="n">
         <v>0</v>
       </c>
       <c r="I2142" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2142" t="inlineStr">
         <is>
@@ -95959,41 +95959,41 @@
     <row r="2143">
       <c r="A2143" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2143" t="inlineStr">
         <is>
-          <t>DG11009</t>
+          <t>DG08002</t>
         </is>
       </c>
       <c r="C2143" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.047</t>
         </is>
       </c>
       <c r="D2143" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2143" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2143" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2143" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2143" t="n">
         <v>0</v>
       </c>
       <c r="I2143" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2143" t="inlineStr">
         <is>
@@ -96004,41 +96004,41 @@
     <row r="2144">
       <c r="A2144" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2144" t="inlineStr">
         <is>
-          <t>DG11010</t>
+          <t>DG08003</t>
         </is>
       </c>
       <c r="C2144" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.048</t>
         </is>
       </c>
       <c r="D2144" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2144" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2144" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2144" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2144" t="n">
         <v>0</v>
       </c>
       <c r="I2144" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2144" t="inlineStr">
         <is>
@@ -96049,17 +96049,17 @@
     <row r="2145">
       <c r="A2145" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2145" t="inlineStr">
         <is>
-          <t>DG11010</t>
+          <t>DG11005</t>
         </is>
       </c>
       <c r="C2145" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.096</t>
         </is>
       </c>
       <c r="D2145" t="inlineStr">
@@ -96094,22 +96094,22 @@
     <row r="2146">
       <c r="A2146" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2146" t="inlineStr">
         <is>
-          <t>DG11011</t>
+          <t>DG12003</t>
         </is>
       </c>
       <c r="C2146" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.145</t>
         </is>
       </c>
       <c r="D2146" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2146" t="n">
@@ -96139,22 +96139,22 @@
     <row r="2147">
       <c r="A2147" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2147" t="inlineStr">
         <is>
-          <t>DG11011</t>
+          <t>DG12004</t>
         </is>
       </c>
       <c r="C2147" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="D2147" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2147" t="n">
@@ -96170,7 +96170,7 @@
         <v>0</v>
       </c>
       <c r="I2147" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2147" t="n">
         <v>3</v>
@@ -96184,22 +96184,22 @@
     <row r="2148">
       <c r="A2148" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2148" t="inlineStr">
         <is>
-          <t>DG11012</t>
+          <t>DG12005</t>
         </is>
       </c>
       <c r="C2148" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.078</t>
         </is>
       </c>
       <c r="D2148" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2148" t="n">
@@ -96229,41 +96229,41 @@
     <row r="2149">
       <c r="A2149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2149" t="inlineStr">
         <is>
-          <t>DG11012</t>
+          <t>DG08004</t>
         </is>
       </c>
       <c r="C2149" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.047</t>
         </is>
       </c>
       <c r="D2149" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2149" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2149" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2149" t="n">
         <v>0</v>
       </c>
       <c r="I2149" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2149" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2149" t="inlineStr">
         <is>
@@ -96274,41 +96274,41 @@
     <row r="2150">
       <c r="A2150" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2150" t="inlineStr">
         <is>
-          <t>DG11013</t>
+          <t>DG08005</t>
         </is>
       </c>
       <c r="C2150" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>3.046</t>
         </is>
       </c>
       <c r="D2150" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2150" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2150" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2150" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2150" t="n">
         <v>0</v>
       </c>
       <c r="I2150" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2150" t="inlineStr">
         <is>
@@ -96319,41 +96319,41 @@
     <row r="2151">
       <c r="A2151" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2151" t="inlineStr">
         <is>
-          <t>DG11013</t>
+          <t>DG08006</t>
         </is>
       </c>
       <c r="C2151" t="inlineStr">
         <is>
-          <t>3.103</t>
+          <t>1.855</t>
         </is>
       </c>
       <c r="D2151" t="inlineStr">
         <is>
-          <t>MN1</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2151" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F2151" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2151" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2151" t="n">
         <v>0</v>
       </c>
       <c r="I2151" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2151" t="inlineStr">
         <is>
@@ -96364,17 +96364,17 @@
     <row r="2152">
       <c r="A2152" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2152" t="inlineStr">
         <is>
-          <t>DG11014</t>
+          <t>DG11012</t>
         </is>
       </c>
       <c r="C2152" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2152" t="inlineStr">
@@ -96395,7 +96395,7 @@
         <v>0</v>
       </c>
       <c r="I2152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2152" t="n">
         <v>3</v>
@@ -96414,12 +96414,12 @@
       </c>
       <c r="B2153" t="inlineStr">
         <is>
-          <t>DG11014</t>
+          <t>DG11013</t>
         </is>
       </c>
       <c r="C2153" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2153" t="inlineStr">
@@ -96454,17 +96454,17 @@
     <row r="2154">
       <c r="A2154" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2154" t="inlineStr">
         <is>
-          <t>DG11015</t>
+          <t>DG11014</t>
         </is>
       </c>
       <c r="C2154" t="inlineStr">
         <is>
-          <t>0.450</t>
+          <t>3.036</t>
         </is>
       </c>
       <c r="D2154" t="inlineStr">
@@ -96476,7 +96476,7 @@
         <v>0</v>
       </c>
       <c r="F2154" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G2154" t="n">
         <v>0</v>
@@ -96485,10 +96485,10 @@
         <v>0</v>
       </c>
       <c r="I2154" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J2154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2154" t="inlineStr">
         <is>
@@ -96499,29 +96499,29 @@
     <row r="2155">
       <c r="A2155" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2155" t="inlineStr">
         <is>
-          <t>DG12003</t>
+          <t>DG11015</t>
         </is>
       </c>
       <c r="C2155" t="inlineStr">
         <is>
-          <t>3.145</t>
+          <t>0.450</t>
         </is>
       </c>
       <c r="D2155" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2155" t="n">
         <v>0</v>
       </c>
       <c r="F2155" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G2155" t="n">
         <v>0</v>
@@ -96530,10 +96530,10 @@
         <v>0</v>
       </c>
       <c r="I2155" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J2155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2155" t="inlineStr">
         <is>
@@ -96544,22 +96544,22 @@
     <row r="2156">
       <c r="A2156" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2156" t="inlineStr">
         <is>
-          <t>DG12004</t>
+          <t>DG35001</t>
         </is>
       </c>
       <c r="C2156" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>3.029</t>
         </is>
       </c>
       <c r="D2156" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2156" t="n">
@@ -96575,10 +96575,10 @@
         <v>0</v>
       </c>
       <c r="I2156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2156" t="inlineStr">
         <is>
@@ -96589,22 +96589,22 @@
     <row r="2157">
       <c r="A2157" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2157" t="inlineStr">
         <is>
-          <t>DG12005</t>
+          <t>DG35002</t>
         </is>
       </c>
       <c r="C2157" t="inlineStr">
         <is>
-          <t>3.078</t>
+          <t>3.017</t>
         </is>
       </c>
       <c r="D2157" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2157" t="n">
@@ -96620,7 +96620,7 @@
         <v>0</v>
       </c>
       <c r="I2157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2157" t="n">
         <v>3</v>
@@ -96634,22 +96634,22 @@
     <row r="2158">
       <c r="A2158" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2158" t="inlineStr">
         <is>
-          <t>DG12006</t>
+          <t>DG35003</t>
         </is>
       </c>
       <c r="C2158" t="inlineStr">
         <is>
-          <t>3.077</t>
+          <t>3.041</t>
         </is>
       </c>
       <c r="D2158" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2158" t="n">
@@ -96665,7 +96665,7 @@
         <v>0</v>
       </c>
       <c r="I2158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2158" t="n">
         <v>3</v>
@@ -96679,29 +96679,29 @@
     <row r="2159">
       <c r="A2159" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2159" t="inlineStr">
         <is>
-          <t>DG12007</t>
+          <t>DG35004</t>
         </is>
       </c>
       <c r="C2159" t="inlineStr">
         <is>
-          <t>3.158</t>
+          <t>0.671</t>
         </is>
       </c>
       <c r="D2159" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2159" t="n">
         <v>0</v>
       </c>
       <c r="F2159" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2159" t="n">
         <v>0</v>
@@ -96710,10 +96710,10 @@
         <v>0</v>
       </c>
       <c r="I2159" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J2159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2159" t="inlineStr">
         <is>
@@ -96724,41 +96724,41 @@
     <row r="2160">
       <c r="A2160" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2160" t="inlineStr">
         <is>
-          <t>DG12008</t>
+          <t>DG29001</t>
         </is>
       </c>
       <c r="C2160" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>2.812</t>
         </is>
       </c>
       <c r="D2160" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2160" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2160" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2160" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2160" t="n">
         <v>0</v>
       </c>
       <c r="I2160" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2160" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2160" t="inlineStr">
         <is>
@@ -96769,38 +96769,38 @@
     <row r="2161">
       <c r="A2161" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2161" t="inlineStr">
         <is>
-          <t>DG16000</t>
+          <t>DG29002</t>
         </is>
       </c>
       <c r="C2161" t="inlineStr">
         <is>
-          <t>4.195</t>
+          <t>2.807</t>
         </is>
       </c>
       <c r="D2161" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2161" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2161" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G2161" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2161" t="n">
         <v>0</v>
       </c>
       <c r="I2161" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J2161" t="n">
         <v>4</v>
@@ -96814,41 +96814,41 @@
     <row r="2162">
       <c r="A2162" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2162" t="inlineStr">
         <is>
-          <t>DG09011</t>
+          <t>DG29003</t>
         </is>
       </c>
       <c r="C2162" t="inlineStr">
         <is>
-          <t>1.890</t>
+          <t>2.804</t>
         </is>
       </c>
       <c r="D2162" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2162" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F2162" t="n">
         <v>0</v>
       </c>
       <c r="G2162" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2162" t="n">
         <v>4</v>
-      </c>
-      <c r="H2162" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2162" t="n">
-        <v>3</v>
       </c>
       <c r="K2162" t="inlineStr">
         <is>
@@ -96859,29 +96859,29 @@
     <row r="2163">
       <c r="A2163" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2163" t="inlineStr">
         <is>
-          <t>DG09011</t>
+          <t>DG11009</t>
         </is>
       </c>
       <c r="C2163" t="inlineStr">
         <is>
-          <t>1.890</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2163" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2163" t="n">
         <v>0</v>
       </c>
       <c r="F2163" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2163" t="n">
         <v>0</v>
@@ -96890,10 +96890,10 @@
         <v>0</v>
       </c>
       <c r="I2163" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J2163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2163" t="inlineStr">
         <is>
@@ -96904,22 +96904,22 @@
     <row r="2164">
       <c r="A2164" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2164" t="inlineStr">
         <is>
-          <t>DG37001</t>
+          <t>DG11010</t>
         </is>
       </c>
       <c r="C2164" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2164" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2164" t="n">
@@ -96935,7 +96935,7 @@
         <v>0</v>
       </c>
       <c r="I2164" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2164" t="n">
         <v>3</v>
@@ -96949,22 +96949,22 @@
     <row r="2165">
       <c r="A2165" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2165" t="inlineStr">
         <is>
-          <t>DG37002</t>
+          <t>DG11011</t>
         </is>
       </c>
       <c r="C2165" t="inlineStr">
         <is>
-          <t>3.035</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2165" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2165" t="n">
@@ -96980,7 +96980,7 @@
         <v>0</v>
       </c>
       <c r="I2165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2165" t="n">
         <v>3</v>
@@ -96994,17 +96994,17 @@
     <row r="2166">
       <c r="A2166" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2166" t="inlineStr">
         <is>
-          <t>DG37003</t>
+          <t>DG04001</t>
         </is>
       </c>
       <c r="C2166" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>3.096</t>
         </is>
       </c>
       <c r="D2166" t="inlineStr">
@@ -97019,7 +97019,7 @@
         <v>6</v>
       </c>
       <c r="G2166" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2166" t="n">
         <v>0</v>
@@ -97028,7 +97028,7 @@
         <v>7</v>
       </c>
       <c r="J2166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2166" t="inlineStr">
         <is>
@@ -97039,17 +97039,17 @@
     <row r="2167">
       <c r="A2167" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2167" t="inlineStr">
         <is>
-          <t>DG37004</t>
+          <t>DG04002</t>
         </is>
       </c>
       <c r="C2167" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>3.105</t>
         </is>
       </c>
       <c r="D2167" t="inlineStr">
@@ -97061,19 +97061,19 @@
         <v>0</v>
       </c>
       <c r="F2167" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G2167" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2167" t="n">
         <v>0</v>
       </c>
       <c r="I2167" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2167" t="n">
         <v>4</v>
-      </c>
-      <c r="J2167" t="n">
-        <v>2</v>
       </c>
       <c r="K2167" t="inlineStr">
         <is>
@@ -97084,22 +97084,22 @@
     <row r="2168">
       <c r="A2168" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2168" t="inlineStr">
         <is>
-          <t>DG01001</t>
+          <t>DG04003</t>
         </is>
       </c>
       <c r="C2168" t="inlineStr">
         <is>
-          <t>3.008</t>
+          <t>3.100</t>
         </is>
       </c>
       <c r="D2168" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2168" t="n">
@@ -97109,7 +97109,7 @@
         <v>6</v>
       </c>
       <c r="G2168" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2168" t="n">
         <v>0</v>
@@ -97118,7 +97118,7 @@
         <v>7</v>
       </c>
       <c r="J2168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2168" t="inlineStr">
         <is>
@@ -97129,41 +97129,41 @@
     <row r="2169">
       <c r="A2169" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2169" t="inlineStr">
         <is>
-          <t>DG01002</t>
+          <t>DG26004</t>
         </is>
       </c>
       <c r="C2169" t="inlineStr">
         <is>
-          <t>3.087</t>
+          <t>2.997</t>
         </is>
       </c>
       <c r="D2169" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2169" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2169" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2169" t="n">
         <v>0</v>
       </c>
       <c r="I2169" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2169" t="inlineStr">
         <is>
@@ -97174,22 +97174,22 @@
     <row r="2170">
       <c r="A2170" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2170" t="inlineStr">
         <is>
-          <t>DG01003</t>
+          <t>DG11001</t>
         </is>
       </c>
       <c r="C2170" t="inlineStr">
         <is>
-          <t>3.042</t>
+          <t>3.056</t>
         </is>
       </c>
       <c r="D2170" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2170" t="n">
@@ -97205,7 +97205,7 @@
         <v>0</v>
       </c>
       <c r="I2170" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2170" t="n">
         <v>3</v>
@@ -97219,22 +97219,22 @@
     <row r="2171">
       <c r="A2171" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2171" t="inlineStr">
         <is>
-          <t>DG01004</t>
+          <t>DG11002</t>
         </is>
       </c>
       <c r="C2171" t="inlineStr">
         <is>
-          <t>3.022</t>
+          <t>3.074</t>
         </is>
       </c>
       <c r="D2171" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2171" t="n">
@@ -97250,7 +97250,7 @@
         <v>0</v>
       </c>
       <c r="I2171" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2171" t="n">
         <v>3</v>
@@ -97264,22 +97264,22 @@
     <row r="2172">
       <c r="A2172" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2172" t="inlineStr">
         <is>
-          <t>DG01005</t>
+          <t>DG11003</t>
         </is>
       </c>
       <c r="C2172" t="inlineStr">
         <is>
-          <t>3.042</t>
+          <t>3.037</t>
         </is>
       </c>
       <c r="D2172" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2172" t="n">
@@ -97295,7 +97295,7 @@
         <v>0</v>
       </c>
       <c r="I2172" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2172" t="n">
         <v>3</v>
@@ -97309,29 +97309,29 @@
     <row r="2173">
       <c r="A2173" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2173" t="inlineStr">
         <is>
-          <t>DG01006</t>
+          <t>DG16000</t>
         </is>
       </c>
       <c r="C2173" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>4.195</t>
         </is>
       </c>
       <c r="D2173" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>97F1692</t>
         </is>
       </c>
       <c r="E2173" t="n">
         <v>0</v>
       </c>
       <c r="F2173" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G2173" t="n">
         <v>0</v>
@@ -97340,10 +97340,10 @@
         <v>0</v>
       </c>
       <c r="I2173" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J2173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2173" t="inlineStr">
         <is>
@@ -97354,29 +97354,29 @@
     <row r="2174">
       <c r="A2174" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2174" t="inlineStr">
         <is>
-          <t>DG01007</t>
+          <t>DG18001</t>
         </is>
       </c>
       <c r="C2174" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.747</t>
         </is>
       </c>
       <c r="D2174" t="inlineStr">
         <is>
-          <t>MIX</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2174" t="n">
         <v>0</v>
       </c>
       <c r="F2174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2174" t="n">
         <v>0</v>
@@ -97385,7 +97385,7 @@
         <v>0</v>
       </c>
       <c r="I2174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2174" t="n">
         <v>2</v>
@@ -97399,22 +97399,22 @@
     <row r="2175">
       <c r="A2175" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2175" t="inlineStr">
         <is>
-          <t>DG02001</t>
+          <t>DG18002</t>
         </is>
       </c>
       <c r="C2175" t="inlineStr">
         <is>
-          <t>2.937</t>
+          <t>3.014</t>
         </is>
       </c>
       <c r="D2175" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2175" t="n">
@@ -97424,7 +97424,7 @@
         <v>6</v>
       </c>
       <c r="G2175" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2175" t="n">
         <v>0</v>
@@ -97433,7 +97433,7 @@
         <v>7</v>
       </c>
       <c r="J2175" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2175" t="inlineStr">
         <is>
@@ -97444,22 +97444,22 @@
     <row r="2176">
       <c r="A2176" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2176" t="inlineStr">
         <is>
-          <t>DG02002</t>
+          <t>DG18003</t>
         </is>
       </c>
       <c r="C2176" t="inlineStr">
         <is>
-          <t>2.942</t>
+          <t>3.101</t>
         </is>
       </c>
       <c r="D2176" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2176" t="n">
@@ -97478,7 +97478,7 @@
         <v>7</v>
       </c>
       <c r="J2176" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2176" t="inlineStr">
         <is>
@@ -97489,22 +97489,22 @@
     <row r="2177">
       <c r="A2177" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2177" t="inlineStr">
         <is>
-          <t>DG02003</t>
+          <t>DG11006</t>
         </is>
       </c>
       <c r="C2177" t="inlineStr">
         <is>
-          <t>3.004</t>
+          <t>3.084</t>
         </is>
       </c>
       <c r="D2177" t="inlineStr">
         <is>
-          <t>97F1692</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2177" t="n">
@@ -97514,16 +97514,16 @@
         <v>6</v>
       </c>
       <c r="G2177" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2177" t="n">
         <v>0</v>
       </c>
       <c r="I2177" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2177" t="inlineStr">
         <is>
@@ -97534,22 +97534,22 @@
     <row r="2178">
       <c r="A2178" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2178" t="inlineStr">
         <is>
-          <t>DG04001</t>
+          <t>DG11007</t>
         </is>
       </c>
       <c r="C2178" t="inlineStr">
         <is>
-          <t>3.096</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2178" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2178" t="n">
@@ -97559,16 +97559,16 @@
         <v>6</v>
       </c>
       <c r="G2178" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2178" t="n">
         <v>0</v>
       </c>
       <c r="I2178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2178" t="inlineStr">
         <is>
@@ -97579,22 +97579,22 @@
     <row r="2179">
       <c r="A2179" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2179" t="inlineStr">
         <is>
-          <t>DG04002</t>
+          <t>DG11008</t>
         </is>
       </c>
       <c r="C2179" t="inlineStr">
         <is>
-          <t>3.105</t>
+          <t>3.103</t>
         </is>
       </c>
       <c r="D2179" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2179" t="n">
@@ -97604,16 +97604,16 @@
         <v>6</v>
       </c>
       <c r="G2179" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2179" t="n">
         <v>0</v>
       </c>
       <c r="I2179" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2179" t="inlineStr">
         <is>
@@ -97624,17 +97624,17 @@
     <row r="2180">
       <c r="A2180" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2180" t="inlineStr">
         <is>
-          <t>DG04003</t>
+          <t>DG04004</t>
         </is>
       </c>
       <c r="C2180" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>3.093</t>
         </is>
       </c>
       <c r="D2180" t="inlineStr">
@@ -97649,7 +97649,7 @@
         <v>6</v>
       </c>
       <c r="G2180" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2180" t="n">
         <v>0</v>
@@ -97658,7 +97658,7 @@
         <v>7</v>
       </c>
       <c r="J2180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2180" t="inlineStr">
         <is>
@@ -97674,12 +97674,12 @@
       </c>
       <c r="B2181" t="inlineStr">
         <is>
-          <t>DG04004</t>
+          <t>DG04005</t>
         </is>
       </c>
       <c r="C2181" t="inlineStr">
         <is>
-          <t>3.093</t>
+          <t>3.064</t>
         </is>
       </c>
       <c r="D2181" t="inlineStr">
@@ -97719,12 +97719,12 @@
       </c>
       <c r="B2182" t="inlineStr">
         <is>
-          <t>DG04005</t>
+          <t>DG04006</t>
         </is>
       </c>
       <c r="C2182" t="inlineStr">
         <is>
-          <t>3.064</t>
+          <t>0.884</t>
         </is>
       </c>
       <c r="D2182" t="inlineStr">
@@ -97736,7 +97736,7 @@
         <v>0</v>
       </c>
       <c r="F2182" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G2182" t="n">
         <v>0</v>
@@ -97745,10 +97745,10 @@
         <v>0</v>
       </c>
       <c r="I2182" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J2182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2182" t="inlineStr">
         <is>
@@ -97764,36 +97764,36 @@
       </c>
       <c r="B2183" t="inlineStr">
         <is>
-          <t>DG04006</t>
+          <t>DG06001</t>
         </is>
       </c>
       <c r="C2183" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>3.036</t>
         </is>
       </c>
       <c r="D2183" t="inlineStr">
         <is>
-          <t>R579</t>
+          <t>R570</t>
         </is>
       </c>
       <c r="E2183" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2183" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2183" t="n">
         <v>0</v>
       </c>
       <c r="I2183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2183" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2183" t="inlineStr">
         <is>
@@ -97804,17 +97804,17 @@
     <row r="2184">
       <c r="A2184" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2184" t="inlineStr">
         <is>
-          <t>DG18001</t>
+          <t>DG06002</t>
         </is>
       </c>
       <c r="C2184" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="D2184" t="inlineStr">
@@ -97823,13 +97823,13 @@
         </is>
       </c>
       <c r="E2184" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F2184" t="n">
         <v>0</v>
       </c>
       <c r="G2184" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2184" t="n">
         <v>0</v>
@@ -97838,7 +97838,7 @@
         <v>0</v>
       </c>
       <c r="J2184" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2184" t="inlineStr">
         <is>
@@ -97849,17 +97849,17 @@
     <row r="2185">
       <c r="A2185" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2185" t="inlineStr">
         <is>
-          <t>DG18001</t>
+          <t>DG06003</t>
         </is>
       </c>
       <c r="C2185" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>3.043</t>
         </is>
       </c>
       <c r="D2185" t="inlineStr">
@@ -97868,22 +97868,22 @@
         </is>
       </c>
       <c r="E2185" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2185" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2185" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2185" t="n">
         <v>0</v>
       </c>
       <c r="I2185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2185" t="n">
         <v>5</v>
-      </c>
-      <c r="J2185" t="n">
-        <v>2</v>
       </c>
       <c r="K2185" t="inlineStr">
         <is>
@@ -97894,41 +97894,41 @@
     <row r="2186">
       <c r="A2186" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2186" t="inlineStr">
         <is>
-          <t>DG18002</t>
+          <t>DG11004</t>
         </is>
       </c>
       <c r="C2186" t="inlineStr">
         <is>
-          <t>3.014</t>
+          <t>1.479</t>
         </is>
       </c>
       <c r="D2186" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>MN1</t>
         </is>
       </c>
       <c r="E2186" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2186" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2186" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2186" t="n">
         <v>0</v>
       </c>
       <c r="I2186" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2186" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2186" t="inlineStr">
         <is>
@@ -97939,22 +97939,22 @@
     <row r="2187">
       <c r="A2187" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2187" t="inlineStr">
         <is>
-          <t>DG18002</t>
+          <t>DG39003</t>
         </is>
       </c>
       <c r="C2187" t="inlineStr">
         <is>
-          <t>3.014</t>
+          <t>2.688</t>
         </is>
       </c>
       <c r="D2187" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2187" t="n">
@@ -97984,22 +97984,22 @@
     <row r="2188">
       <c r="A2188" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2188" t="inlineStr">
         <is>
-          <t>DG18003</t>
+          <t>DG32007</t>
         </is>
       </c>
       <c r="C2188" t="inlineStr">
         <is>
-          <t>3.101</t>
+          <t>3.033</t>
         </is>
       </c>
       <c r="D2188" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2188" t="n">
@@ -98009,13 +98009,13 @@
         <v>6</v>
       </c>
       <c r="G2188" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2188" t="n">
         <v>0</v>
       </c>
       <c r="I2188" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2188" t="n">
         <v>3</v>
@@ -98029,22 +98029,22 @@
     <row r="2189">
       <c r="A2189" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2189" t="inlineStr">
         <is>
-          <t>DG18004</t>
+          <t>DG32006</t>
         </is>
       </c>
       <c r="C2189" t="inlineStr">
         <is>
-          <t>3.109</t>
+          <t>3.047</t>
         </is>
       </c>
       <c r="D2189" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2189" t="n">
@@ -98054,13 +98054,13 @@
         <v>6</v>
       </c>
       <c r="G2189" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2189" t="n">
         <v>0</v>
       </c>
       <c r="I2189" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2189" t="n">
         <v>4</v>
@@ -98074,22 +98074,22 @@
     <row r="2190">
       <c r="A2190" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2190" t="inlineStr">
         <is>
-          <t>DG18005</t>
+          <t>DG31001</t>
         </is>
       </c>
       <c r="C2190" t="inlineStr">
         <is>
-          <t>3.094</t>
+          <t>3.025</t>
         </is>
       </c>
       <c r="D2190" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2190" t="n">
@@ -98099,16 +98099,16 @@
         <v>6</v>
       </c>
       <c r="G2190" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2190" t="n">
         <v>0</v>
       </c>
       <c r="I2190" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2190" t="inlineStr">
         <is>
@@ -98119,41 +98119,41 @@
     <row r="2191">
       <c r="A2191" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2191" t="inlineStr">
         <is>
-          <t>DG08001</t>
+          <t>DG27001</t>
         </is>
       </c>
       <c r="C2191" t="inlineStr">
         <is>
-          <t>3.081</t>
+          <t>3.108</t>
         </is>
       </c>
       <c r="D2191" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2191" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2191" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2191" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2191" t="n">
         <v>0</v>
       </c>
       <c r="I2191" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2191" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2191" t="inlineStr">
         <is>
@@ -98164,41 +98164,41 @@
     <row r="2192">
       <c r="A2192" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2192" t="inlineStr">
         <is>
-          <t>DG08002</t>
+          <t>DG27002</t>
         </is>
       </c>
       <c r="C2192" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>3.126</t>
         </is>
       </c>
       <c r="D2192" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2192" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2192" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2192" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2192" t="n">
         <v>0</v>
       </c>
       <c r="I2192" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2192" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2192" t="inlineStr">
         <is>
@@ -98209,17 +98209,17 @@
     <row r="2193">
       <c r="A2193" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2193" t="inlineStr">
         <is>
-          <t>DG08003</t>
+          <t>DG20001</t>
         </is>
       </c>
       <c r="C2193" t="inlineStr">
         <is>
-          <t>3.048</t>
+          <t>3.032</t>
         </is>
       </c>
       <c r="D2193" t="inlineStr">
@@ -98228,22 +98228,22 @@
         </is>
       </c>
       <c r="E2193" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2193" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2193" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2193" t="n">
         <v>0</v>
       </c>
       <c r="I2193" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2193" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2193" t="inlineStr">
         <is>
@@ -98254,17 +98254,17 @@
     <row r="2194">
       <c r="A2194" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2194" t="inlineStr">
         <is>
-          <t>DG08004</t>
+          <t>DG20002</t>
         </is>
       </c>
       <c r="C2194" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>3.001</t>
         </is>
       </c>
       <c r="D2194" t="inlineStr">
@@ -98273,22 +98273,22 @@
         </is>
       </c>
       <c r="E2194" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2194" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2194" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2194" t="n">
         <v>0</v>
       </c>
       <c r="I2194" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2194" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2194" t="inlineStr">
         <is>
@@ -98299,17 +98299,17 @@
     <row r="2195">
       <c r="A2195" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2195" t="inlineStr">
         <is>
-          <t>DG08005</t>
+          <t>DG20003</t>
         </is>
       </c>
       <c r="C2195" t="inlineStr">
         <is>
-          <t>3.046</t>
+          <t>3.043</t>
         </is>
       </c>
       <c r="D2195" t="inlineStr">
@@ -98318,22 +98318,22 @@
         </is>
       </c>
       <c r="E2195" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2195" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2195" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2195" t="n">
         <v>0</v>
       </c>
       <c r="I2195" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2195" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2195" t="inlineStr">
         <is>
@@ -98344,41 +98344,41 @@
     <row r="2196">
       <c r="A2196" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2196" t="inlineStr">
         <is>
-          <t>DG08006</t>
+          <t>DG27003</t>
         </is>
       </c>
       <c r="C2196" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>3.125</t>
         </is>
       </c>
       <c r="D2196" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2196" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F2196" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2196" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2196" t="n">
         <v>0</v>
       </c>
       <c r="I2196" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2196" t="inlineStr">
         <is>
@@ -98389,41 +98389,41 @@
     <row r="2197">
       <c r="A2197" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2197" t="inlineStr">
         <is>
-          <t>DG06001</t>
+          <t>DG31002</t>
         </is>
       </c>
       <c r="C2197" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>3.026</t>
         </is>
       </c>
       <c r="D2197" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="E2197" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2197" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2197" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2197" t="n">
         <v>0</v>
       </c>
       <c r="I2197" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2197" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2197" t="inlineStr">
         <is>
@@ -98434,12 +98434,12 @@
     <row r="2198">
       <c r="A2198" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2198" t="inlineStr">
         <is>
-          <t>DG06002</t>
+          <t>DG39002</t>
         </is>
       </c>
       <c r="C2198" t="inlineStr">
@@ -98449,26 +98449,26 @@
       </c>
       <c r="D2198" t="inlineStr">
         <is>
-          <t>R570</t>
+          <t>R579</t>
         </is>
       </c>
       <c r="E2198" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2198" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2198" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2198" t="n">
         <v>0</v>
       </c>
       <c r="I2198" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2198" t="inlineStr">
         <is>
@@ -98479,43 +98479,1303 @@
     <row r="2199">
       <c r="A2199" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2199" t="inlineStr">
         <is>
-          <t>DG06003</t>
+          <t>DG18004</t>
         </is>
       </c>
       <c r="C2199" t="inlineStr">
         <is>
+          <t>3.109</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2199" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2199" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2199" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2199" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2199" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>DG18005</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>3.094</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2200" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2200" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2200" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2200" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2200" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>DG36001</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>3.016</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2201" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2201" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2201" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2201" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2201" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>DG36002</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>3.015</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2202" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2202" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2202" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2202" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2202" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>DG26001</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>2.994</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2203" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2203" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2203" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>DG20004</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
           <t>3.043</t>
         </is>
       </c>
-      <c r="D2199" t="inlineStr">
+      <c r="D2204" t="inlineStr">
         <is>
           <t>R570</t>
         </is>
       </c>
-      <c r="E2199" t="n">
-        <v>15</v>
-      </c>
-      <c r="F2199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2199" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2199" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2199" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2199" t="n">
+      <c r="E2204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2204" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2204" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2204" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>DG20005</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>3.044</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2205" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2205" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2205" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>DG27004</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>4.634</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2206" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2206" t="n">
         <v>5</v>
       </c>
-      <c r="K2199" t="inlineStr">
+      <c r="H2206" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2206" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2206" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2206" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>DG31003</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>3.026</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2207" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2207" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2207" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>DG31004</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>3.026</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2208" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2208" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2208" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>DG39001</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>3.024</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2209" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2209" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2209" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>DG20006</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>3.042</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2210" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2210" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2210" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>DG20007</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>3.039</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2211" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2211" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2211" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>DG20008</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>1.668</t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2212" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2212" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2212" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>DG36003</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>3.016</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2213" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2213" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2213" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2213" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2213" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>DG36004</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>2.078</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2214" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2214" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2214" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2214" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>DG26004</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>0.450</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2215" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>DG32001</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>3.006</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2216" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2216" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2216" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>DG32002</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>3.009</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2217" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2217" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2217" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>DG31005</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>3.025</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2218" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2218" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2218" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2218" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>DG31006</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>3.025</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2219" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2219" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2219" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2219" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>DG31007</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>3.026</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2220" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2220" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2220" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2220" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>DG32003</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>3.019</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2221" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2221" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2221" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2221" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>DG32004</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>3.012</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2222" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2222" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2222" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2222" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>DG32005</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>3.012</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2223" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2223" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2223" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2223" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>DG25001</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>3.097</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2224" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2224" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2224" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2224" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>DG25002</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>3.118</t>
+        </is>
+      </c>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2225" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2225" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2225" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2225" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>DG31008</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>3.023</t>
+        </is>
+      </c>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2226" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2226" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2226" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2226" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>DG31009</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2227" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2227" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2227" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2227"/>
+  <dimension ref="A1:K2282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95159,7 +95159,7 @@
       </c>
       <c r="C2125" t="inlineStr">
         <is>
-          <t>3.0141</t>
+          <t>3.141</t>
         </is>
       </c>
       <c r="D2125" t="inlineStr">
@@ -99776,6 +99776,2481 @@
         <v>1</v>
       </c>
       <c r="K2227" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>DG05006</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>2.227</t>
+        </is>
+      </c>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2228" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2228" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2228" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2228" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>DG06004</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>3.052</t>
+        </is>
+      </c>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2229" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2229" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2229" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2229" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>DG06005</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>3.044</t>
+        </is>
+      </c>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2230" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2230" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2230" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2230" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>DG06006</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>0.238</t>
+        </is>
+      </c>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2231" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2231" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>DG01001</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>3.008</t>
+        </is>
+      </c>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="E2232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2232" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2232" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2232" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>DG01002</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>3.087</t>
+        </is>
+      </c>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="E2233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2233" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2233" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2233" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2233" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>DG01003</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>3.042</t>
+        </is>
+      </c>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="E2234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2234" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2234" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2234" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2234" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>DG13001</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>3.200</t>
+        </is>
+      </c>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2235" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2235" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2235" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2235" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>DG13002</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>3.168</t>
+        </is>
+      </c>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2236" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2236" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2236" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2236" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2236" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>DG13003</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>3.194</t>
+        </is>
+      </c>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2237" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2237" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2237" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2237" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2237" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>DG25003</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>3.136</t>
+        </is>
+      </c>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2238" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2238" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2238" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2238" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2238" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>DG25004</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>3.136</t>
+        </is>
+      </c>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2239" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2239" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2239" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2239" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>DG26008</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>2.997</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2240" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2240" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2240" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>DG26009</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>0.143</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2241" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2241" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2241" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2241" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>DG34001</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>3.011</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="E2242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2242" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2242" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2242" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2242" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>DG34002</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>3.048</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="E2243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2243" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2243" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2243" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>DG09011</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>1.890</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2244" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2244" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2244" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>DG34003</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>3.051</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="E2245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2245" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2245" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2245" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2245" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2245" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>DG26005</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>2.996</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2246" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2246" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2246" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>DG26006</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>2.996</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2247" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2247" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2247" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2247" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2247" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>DG26007</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>2.996</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2248" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2248" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2248" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2248" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2248" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>DG37003</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>3.030</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2249" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2249" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2249" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2249" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>DG37004</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>1.349</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2250" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2250" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2250" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2250" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>DG25005</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>3.141</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2251" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2251" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2251" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2251" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>DG25006</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>2.697</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2252" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2252" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2252" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2252" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>DG13004</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>3.194</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2253" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2253" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2253" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2253" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>DG13005</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>3.189</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2254" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2254" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2254" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2254" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2254" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>DG13006</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>3.175</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2255" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2255" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2255" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2255" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2255" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>DG13007</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>3.187</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2256" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2256" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2256" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2256" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>DG15001</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>3.002</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2257" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2257" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2257" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2257" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2257" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>DG15002</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>3.005</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2258" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2258" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2258" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2258" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>DG15003</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>3.041</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2259" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2259" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2259" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2259" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2259" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>DG37002</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>3.035</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2260" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2260" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2260" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2260" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>DG34004</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>3.019</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="E2261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2261" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2261" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2261" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2261" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>DG34005</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>0.449</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="E2262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2262" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2262" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>DG13008</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>3.180</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2263" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2263" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2263" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2263" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>DG13009</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>3.177</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2264" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2264" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2264" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2264" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>DG13010</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>3.154</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2265" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2265" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2265" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2265" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>DG13011</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>3.134</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2266" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2266" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2266" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2266" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>DG13012</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2267" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2267" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2267" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>DG15004</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>3.026</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2268" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2268" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2268" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>DG15005</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>3.015</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2269" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2269" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2269" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>DG15006</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2270" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2270" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2270" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>DG26002</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>2.992</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2271" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2271" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2271" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2271" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>DG02001</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>2.937</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="E2272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2272" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2272" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2272" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2272" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>DG02002</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>2.942</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="E2273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2273" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2273" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2273" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2273" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>DG02003</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>3.004</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="E2274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2274" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2274" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2274" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2274" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2274" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>DG37001</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>3.025</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2275" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2275" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2275" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2275" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>DG38003</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>1.124</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2276" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2276" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2276" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>DG08001</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>3.081</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2277" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2277" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2277" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>DG08002</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>3.047</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2278" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2278" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2278" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2278" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2278" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>DG08003</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>3.048</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2279" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2279" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2279" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2279" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>DG15007</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>3.027</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2280" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2280" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2280" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>DG15008</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>3.003</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2281" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2281" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2281" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>DG15009</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>0.289</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2282" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2282" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2282" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2282" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2282" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2282"/>
+  <dimension ref="A1:K2292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88604,7 +88604,7 @@
         <v>0</v>
       </c>
       <c r="G1979" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1979" t="n">
         <v>0</v>
@@ -101204,7 +101204,7 @@
         <v>0</v>
       </c>
       <c r="G2259" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2259" t="n">
         <v>0</v>
@@ -102251,6 +102251,456 @@
         <v>1</v>
       </c>
       <c r="K2282" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>DG01004</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>3.022</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="E2283" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2283" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2283" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2283" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2283" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>DG01005</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>3.042</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="E2284" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2284" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2284" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2284" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2284" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>DG01006</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>3.040</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="E2285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2285" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2285" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2285" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>DG01007</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>1.445</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="E2286" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2286" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2286" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2286" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2286" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2286" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>DG08004</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>3.047</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2287" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2287" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2287" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2287" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2287" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>DG08005</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>3.046</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2288" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2288" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2288" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2288" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2288" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>DG08006</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>1.855</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="E2289" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2289" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2289" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2289" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2289" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2289" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>DG12002</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>3.122</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2290" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2290" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2290" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2290" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2290" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>DG12001</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>3.123</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2291" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2291" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2291" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2291" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2291" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2291" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>DG04001</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>3.096</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2292" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2292" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2292" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2292" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2292" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2292"/>
+  <dimension ref="A1:K2316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102706,6 +102706,1086 @@
         </is>
       </c>
     </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>DG04002</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>3.035</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2293" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2293" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2293" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2293" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>DG04003</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>3.100</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2294" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2294" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2294" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2294" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>DG04004</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>3.093</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2295" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2295" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2295" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2295" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2295" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>DG04005</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>3.001</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2296" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2296" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2296" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2296" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2296" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2296" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>DG04006</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2297" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2297" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2297" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2297" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2297" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>DG33001</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>3.055</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2298" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2298" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2298" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2298" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>DG33002</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>3.127</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2299" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2299" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2299" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2299" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>DG33003</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>3.089</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2300" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2300" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2300" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2300" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2300" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>DG33004</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>3.099</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2301" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2301" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2301" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2301" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>DG33005</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2302" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2302" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2302" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2302" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>DG33006</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2303" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2303" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2303" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2303" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>DG33007</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2304" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2304" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2304" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2304" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>DG33008</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2305" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2305" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2305" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2305" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>DG26003</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2306" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2306" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2306" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2306" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2306" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2306" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>DG26004</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2307" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2307" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2307" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2307" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2307" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>DG22003</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>3.019</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2308" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2308" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2308" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2308" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>DG22004</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>3.054</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2309" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2309" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2309" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2309" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>DG22005</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>3.055</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2310" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2310" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2310" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2310" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>DG22006</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>3.064</t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2311" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2311" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2311" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2311" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2311" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>DG22007</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>3.071</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2312" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2312" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2312" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2312" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2312" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>DG22008</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>3.049</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2313" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2313" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2313" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>DG22007</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>3.071</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2314" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2314" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2314" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2314" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2314" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2314" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2314" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>DG22008</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>3.049</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2315" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2315" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2315" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2315" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2315" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2315" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>DG22009</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>0.362</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2316" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2316" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2316" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2316" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2316" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2316" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2316" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2316"/>
+  <dimension ref="A1:K2323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103786,6 +103786,321 @@
         </is>
       </c>
     </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>DG22006</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>3.064</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2317" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2317" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2317" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2317" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2317" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>DG22005</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>3.055</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2318" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2318" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2318" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2318" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2318" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2318" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2318" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>DG22004</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>3.054</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2319" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2319" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2319" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2319" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2319" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2319" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>DG22003</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>3.046</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="E2320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2320" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2320" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2320" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2320" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2320" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>DG17001</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>3.077</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2321" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2321" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2321" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2321" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2321" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2321" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>DG17002</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2322" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2322" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2322" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2322" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2322" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2322" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>DG17003</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>3.037</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="E2323" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2323" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2323" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2323" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2323" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
